--- a/output/roomself_excel/4990.xlsx
+++ b/output/roomself_excel/4990.xlsx
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14960</v>
+        <v>212395</v>
       </c>
       <c r="D2" t="n">
-        <v>1656</v>
+        <v>3864</v>
       </c>
       <c r="E2" t="n">
-        <v>390</v>
+        <v>493</v>
       </c>
       <c r="F2" t="n">
-        <v>56</v>
+        <v>461</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>164518</v>
+        <v>303401</v>
       </c>
       <c r="D3" t="n">
-        <v>3588</v>
+        <v>5120</v>
       </c>
       <c r="E3" t="n">
-        <v>467</v>
+        <v>741</v>
       </c>
       <c r="F3" t="n">
-        <v>406</v>
+        <v>470</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>126978</v>
+        <v>164518</v>
       </c>
       <c r="D4" t="n">
-        <v>4220</v>
+        <v>3588</v>
       </c>
       <c r="E4" t="n">
-        <v>895</v>
+        <v>395</v>
       </c>
       <c r="F4" t="n">
-        <v>257</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>212395</v>
+        <v>177627</v>
       </c>
       <c r="D5" t="n">
-        <v>3864</v>
+        <v>3592</v>
       </c>
       <c r="E5" t="n">
-        <v>493</v>
+        <v>569</v>
       </c>
       <c r="F5" t="n">
-        <v>461</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>92156</v>
+        <v>148630</v>
       </c>
       <c r="D6" t="n">
-        <v>3184</v>
+        <v>3116</v>
       </c>
       <c r="E6" t="n">
-        <v>505</v>
+        <v>461</v>
       </c>
       <c r="F6" t="n">
-        <v>496</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>30633</v>
+        <v>24416</v>
       </c>
       <c r="D7" t="n">
-        <v>1536</v>
+        <v>1320</v>
       </c>
       <c r="E7" t="n">
-        <v>239</v>
+        <v>112</v>
       </c>
       <c r="F7" t="n">
-        <v>193</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8700</v>
+        <v>21240</v>
       </c>
       <c r="D8" t="n">
-        <v>764</v>
+        <v>1304</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>80344</v>
+        <v>126978</v>
       </c>
       <c r="D9" t="n">
-        <v>2296</v>
+        <v>4220</v>
       </c>
       <c r="E9" t="n">
-        <v>364</v>
+        <v>241</v>
       </c>
       <c r="F9" t="n">
-        <v>274</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12978</v>
+        <v>92156</v>
       </c>
       <c r="D10" t="n">
-        <v>916</v>
+        <v>3184</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>505</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>24416</v>
+        <v>47955</v>
       </c>
       <c r="D11" t="n">
-        <v>1320</v>
+        <v>1936</v>
       </c>
       <c r="E11" t="n">
-        <v>518</v>
+        <v>139</v>
       </c>
       <c r="F11" t="n">
-        <v>72</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2200</v>
+        <v>255240</v>
       </c>
       <c r="D12" t="n">
-        <v>376</v>
+        <v>4276</v>
       </c>
       <c r="E12" t="n">
-        <v>44</v>
+        <v>724</v>
       </c>
       <c r="F12" t="n">
-        <v>16</v>
+        <v>392</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>303401</v>
+        <v>14960</v>
       </c>
       <c r="D13" t="n">
-        <v>5120</v>
+        <v>1656</v>
       </c>
       <c r="E13" t="n">
-        <v>1357</v>
+        <v>390</v>
       </c>
       <c r="F13" t="n">
-        <v>847</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14">
@@ -734,16 +734,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9718</v>
+        <v>30633</v>
       </c>
       <c r="D14" t="n">
-        <v>796</v>
+        <v>1536</v>
       </c>
       <c r="E14" t="n">
-        <v>113</v>
+        <v>239</v>
       </c>
       <c r="F14" t="n">
-        <v>16</v>
+        <v>193</v>
       </c>
     </row>
     <row r="15">
@@ -752,20 +752,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>177627</v>
+        <v>8700</v>
       </c>
       <c r="D15" t="n">
-        <v>3592</v>
+        <v>764</v>
       </c>
       <c r="E15" t="n">
-        <v>569</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>248</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -774,20 +774,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>47955</v>
+        <v>80344</v>
       </c>
       <c r="D16" t="n">
-        <v>1936</v>
+        <v>2296</v>
       </c>
       <c r="E16" t="n">
-        <v>139</v>
+        <v>364</v>
       </c>
       <c r="F16" t="n">
-        <v>16</v>
+        <v>274</v>
       </c>
     </row>
     <row r="17">
@@ -796,20 +796,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21240</v>
+        <v>12978</v>
       </c>
       <c r="D17" t="n">
-        <v>1304</v>
+        <v>916</v>
       </c>
       <c r="E17" t="n">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -822,16 +822,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>118775</v>
+        <v>2200</v>
       </c>
       <c r="D18" t="n">
-        <v>4227</v>
+        <v>376</v>
       </c>
       <c r="E18" t="n">
-        <v>847</v>
+        <v>44</v>
       </c>
       <c r="F18" t="n">
-        <v>366</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
@@ -844,16 +844,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2701</v>
+        <v>9718</v>
       </c>
       <c r="D19" t="n">
-        <v>440</v>
+        <v>796</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -866,16 +866,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>47520</v>
+        <v>118775</v>
       </c>
       <c r="D20" t="n">
-        <v>1968</v>
+        <v>4227</v>
       </c>
       <c r="E20" t="n">
-        <v>392</v>
+        <v>370</v>
       </c>
       <c r="F20" t="n">
-        <v>148</v>
+        <v>203</v>
       </c>
     </row>
     <row r="21">
@@ -884,20 +884,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>255240</v>
+        <v>2701</v>
       </c>
       <c r="D21" t="n">
-        <v>4276</v>
+        <v>440</v>
       </c>
       <c r="E21" t="n">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>392</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -906,20 +906,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>148630</v>
+        <v>47520</v>
       </c>
       <c r="D22" t="n">
-        <v>3116</v>
+        <v>1968</v>
       </c>
       <c r="E22" t="n">
-        <v>461</v>
+        <v>392</v>
       </c>
       <c r="F22" t="n">
-        <v>350</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/4990.xlsx
+++ b/output/roomself_excel/4990.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,11 +495,27 @@
       <c r="D2" t="n">
         <v>3864</v>
       </c>
-      <c r="E2" t="n">
-        <v>493</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>461</v>
+        <v>477</v>
+      </c>
+      <c r="G2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>429</v>
+      </c>
+      <c r="J2" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -497,12 +533,20 @@
       <c r="D3" t="n">
         <v>5120</v>
       </c>
-      <c r="E3" t="n">
-        <v>741</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>470</v>
-      </c>
+        <v>851</v>
+      </c>
+      <c r="G3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +563,20 @@
       <c r="D4" t="n">
         <v>3588</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>395</v>
       </c>
-      <c r="F4" t="n">
-        <v>16</v>
-      </c>
+      <c r="G4" t="n">
+        <v>16</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,11 +593,27 @@
       <c r="D5" t="n">
         <v>3592</v>
       </c>
-      <c r="E5" t="n">
-        <v>569</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>248</v>
+        <v>216</v>
+      </c>
+      <c r="G5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>553</v>
+      </c>
+      <c r="J5" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -563,11 +631,27 @@
       <c r="D6" t="n">
         <v>3116</v>
       </c>
-      <c r="E6" t="n">
-        <v>461</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>350</v>
+        <v>334</v>
+      </c>
+      <c r="G6" t="n">
+        <v>16</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>445</v>
+      </c>
+      <c r="J6" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -585,12 +669,20 @@
       <c r="D7" t="n">
         <v>1320</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>112</v>
       </c>
-      <c r="F7" t="n">
-        <v>16</v>
-      </c>
+      <c r="G7" t="n">
+        <v>16</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,11 +699,27 @@
       <c r="D8" t="n">
         <v>1304</v>
       </c>
-      <c r="E8" t="n">
-        <v>252</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>106</v>
+        <v>90</v>
+      </c>
+      <c r="G8" t="n">
+        <v>16</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>236</v>
+      </c>
+      <c r="J8" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -629,11 +737,27 @@
       <c r="D9" t="n">
         <v>4220</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>241</v>
       </c>
-      <c r="F9" t="n">
-        <v>16</v>
+      <c r="G9" t="n">
+        <v>16</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>486</v>
+      </c>
+      <c r="J9" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="10">
@@ -651,11 +775,27 @@
       <c r="D10" t="n">
         <v>3184</v>
       </c>
-      <c r="E10" t="n">
-        <v>505</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>232</v>
+        <v>216</v>
+      </c>
+      <c r="G10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>457</v>
+      </c>
+      <c r="J10" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -673,10 +813,26 @@
       <c r="D11" t="n">
         <v>1936</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>345</v>
+      </c>
+      <c r="G11" t="n">
+        <v>14</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>139</v>
       </c>
-      <c r="F11" t="n">
+      <c r="J11" t="n">
         <v>16</v>
       </c>
     </row>
@@ -695,11 +851,27 @@
       <c r="D12" t="n">
         <v>4276</v>
       </c>
-      <c r="E12" t="n">
-        <v>724</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>392</v>
+        <v>1418</v>
+      </c>
+      <c r="G12" t="n">
+        <v>16</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>360</v>
+      </c>
+      <c r="J12" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -717,11 +889,27 @@
       <c r="D13" t="n">
         <v>1656</v>
       </c>
-      <c r="E13" t="n">
-        <v>390</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>56</v>
+        <v>40</v>
+      </c>
+      <c r="G13" t="n">
+        <v>16</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>374</v>
+      </c>
+      <c r="J13" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="14">
@@ -739,11 +927,27 @@
       <c r="D14" t="n">
         <v>1536</v>
       </c>
-      <c r="E14" t="n">
-        <v>239</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>193</v>
+        <v>282</v>
+      </c>
+      <c r="G14" t="n">
+        <v>16</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>338</v>
+      </c>
+      <c r="J14" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -761,12 +965,12 @@
       <c r="D15" t="n">
         <v>764</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,11 +987,27 @@
       <c r="D16" t="n">
         <v>2296</v>
       </c>
-      <c r="E16" t="n">
-        <v>364</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>274</v>
+        <v>352</v>
+      </c>
+      <c r="G16" t="n">
+        <v>16</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>664</v>
+      </c>
+      <c r="J16" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="17">
@@ -805,12 +1025,12 @@
       <c r="D17" t="n">
         <v>916</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +1047,20 @@
       <c r="D18" t="n">
         <v>376</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
         <v>44</v>
       </c>
-      <c r="F18" t="n">
-        <v>16</v>
-      </c>
+      <c r="G18" t="n">
+        <v>16</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +1077,20 @@
       <c r="D19" t="n">
         <v>796</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
         <v>113</v>
       </c>
-      <c r="F19" t="n">
-        <v>16</v>
-      </c>
+      <c r="G19" t="n">
+        <v>16</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,11 +1107,27 @@
       <c r="D20" t="n">
         <v>4227</v>
       </c>
-      <c r="E20" t="n">
-        <v>370</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F20" t="n">
-        <v>203</v>
+        <v>171</v>
+      </c>
+      <c r="G20" t="n">
+        <v>16</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>338</v>
+      </c>
+      <c r="J20" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -893,12 +1145,12 @@
       <c r="D21" t="n">
         <v>440</v>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -915,11 +1167,27 @@
       <c r="D22" t="n">
         <v>1968</v>
       </c>
-      <c r="E22" t="n">
-        <v>392</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F22" t="n">
-        <v>148</v>
+        <v>264</v>
+      </c>
+      <c r="G22" t="n">
+        <v>16</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>360</v>
+      </c>
+      <c r="J22" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
